--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-06).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-06).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>22</t>
+    <t>18</t>
   </si>
   <si>
-    <t>R$ 9.663,91</t>
+    <t>R$ 9.625,00</t>
   </si>
   <si>
-    <t>102.0</t>
+    <t>101.6</t>
   </si>
   <si>
     <t>68.0</t>
   </si>
   <si>
-    <t>7.62</t>
+    <t>7.68</t>
   </si>
   <si>
-    <t>23.4</t>
+    <t>23.5</t>
   </si>
   <si>
-    <t>9.0</t>
+    <t>9.1</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>27.3%</t>
+    <t>27.4%</t>
   </si>
   <si>
-    <t>18.4%</t>
+    <t>18.3%</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -980,19 +980,16 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>6.4%</t>
+    <t>6.3%</t>
   </si>
   <si>
     <t>2.2%</t>
   </si>
   <si>
-    <t>6.3%</t>
+    <t>2744.0</t>
   </si>
   <si>
-    <t>2743.0</t>
-  </si>
-  <si>
-    <t>2352.0</t>
+    <t>2353.0</t>
   </si>
   <si>
     <t>170.0</t>
@@ -1001,7 +998,7 @@
     <t>88.0</t>
   </si>
   <si>
-    <t>404.0</t>
+    <t>405.0</t>
   </si>
   <si>
     <t>134.0</t>
@@ -4965,7 +4962,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4995,14 +4992,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>12290.639999999999</v>
+      </c>
+      <c r="N24" s="6">
+        <v>145</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>7.3421298611111103</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>23.643421052631577</v>
+      </c>
+      <c r="R24" s="8">
+        <v>9.1071640350877185</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.096491228070175433</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6789,7 +6798,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6819,14 +6828,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>6546.5699999999997</v>
+      </c>
+      <c r="N36" s="6">
+        <v>73</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>12.027083333333334</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>25.384794736842103</v>
+      </c>
+      <c r="R36" s="8">
+        <v>5.3654767857142858</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.19298245614035087</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9078,7 +9099,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9108,14 +9129,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1439.7</v>
+      </c>
+      <c r="N51" s="6">
+        <v>11</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>1.9318181818181819</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>29.175000000000001</v>
+      </c>
+      <c r="R51" s="8">
+        <v>20.162500000000001</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0.125</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14780,7 +14813,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14808,14 +14841,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>10790.99</v>
+      </c>
+      <c r="N89" s="6">
+        <v>94</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>22.077239784946237</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>47.693421052631578</v>
+      </c>
+      <c r="R89" s="8">
+        <v>20.142647058823531</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.078947368421052627</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -28448,7 +28493,9 @@
       <c r="N179" s="6">
         <v>146</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>57</v>
+      </c>
       <c r="P179" s="7">
         <v>5.4770547945205479</v>
       </c>
@@ -28458,31 +28505,75 @@
       <c r="R179" s="8">
         <v>2.8812859649122808</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.43859649122807015</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
@@ -33708,43 +33799,43 @@
         <v>324</v>
       </c>
       <c t="s" r="AC216" s="11">
+        <v>323</v>
+      </c>
+      <c t="s" r="AD216" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AE216" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AF216" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AG216" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AH216" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AI216" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AJ216" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AK216" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AL216" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AM216" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AN216" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AO216" s="11">
         <v>336</v>
-      </c>
-      <c t="s" r="AO216" s="11">
-        <v>337</v>
       </c>
       <c r="AP216" s="12"/>
       <c t="s" r="AQ216" s="12">
@@ -33761,10 +33852,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX216" s="11">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c t="s" r="AY216" s="11">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AZ216" s="12"/>
       <c r="BA216" s="12"/>
